--- a/function/functionList_appCore.xlsx
+++ b/function/functionList_appCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\function\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93136520-644A-4DBA-8A8C-78DCC7641998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84983F01-BA8A-4C58-B7C4-126E8A5A16C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elenco funzioni" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
   <si>
     <t>Codice</t>
   </si>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t>YVBPC / YAX3MVBP</t>
+  </si>
+  <si>
+    <t>YAX3MVXP</t>
+  </si>
+  <si>
+    <t>Picking List</t>
   </si>
 </sst>
 </file>
@@ -204,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,12 +230,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,17 +512,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="41.88671875" customWidth="1"/>
-    <col min="6" max="6" width="82.33203125" customWidth="1"/>
+    <col min="5" max="5" width="41.85546875" customWidth="1"/>
+    <col min="6" max="6" width="82.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -542,8 +542,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -552,15 +552,15 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -569,15 +569,15 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -586,15 +586,15 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -603,14 +603,14 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -644,7 +644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -661,7 +661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -678,7 +678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -695,19 +695,33 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F15" s="5"/>
     </row>
   </sheetData>
